--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_NJ.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_NJ.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R3fa63d0177674871"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R7e81bdeabd2e4776"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rd38bcfe4f94b42bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R9d5e3d98edb745ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R605236d391264715"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R07ca0fd26a0e4bb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R42b13e83a8734cbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R2866b1c990c14a0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Rc9a0e901cde54ed0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R78a0393f1bd54a13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Rfbf03209de9c400f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R30eafb2ce9644cd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R83d0091972af433c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R0567a0c8cb3b47c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rb35fb61579fa451e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R7398e278be9d455a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R7245b948adcc4655"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R50b316c86f4f466a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rc1d8063fe4d64ff2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R5a2e66bb4d7141dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R4422c89c013d404c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R6984c1dc38094c1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rb4913cd1e1e6482d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rc73f8181862f4d69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R25707099c0484fb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R53f0e8b2025f4cc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R769b2d933fec4a62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R17b9ae2c3dec47ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R782d5253fcc8478b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Ra3c856530c0f476a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Ra2f53e9b9bb743a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Ra0b7f485c7e14db9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R46be0217c6b14e52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R68c70e81f7e94c0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rc6cc5e2eaf3440f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rf4c12e5bfdbc49dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R63fa1bea8b5d493c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Ree17ebb9322f45f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Re1ba1ad0a2c74438"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rf75b71bada3a4052"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R9ee42b6bd2c84853"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R803e867fd8ac43dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R50209c4167e94777"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2979,6 +2980,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>龍助(りゅうすけ)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>鳥の国・ナルサワ家門</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
